--- a/diseases/d227/2026-2029.xlsx
+++ b/diseases/d227/2026-2029.xlsx
@@ -13555,13 +13555,13 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>5530</v>
+        <v>5529</v>
       </c>
       <c r="O66" t="n">
-        <v>5530</v>
+        <v>5529</v>
       </c>
       <c r="R66" t="n">
-        <v>10.71697367857001</v>
+        <v>10.71503570864622</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -13714,10 +13714,10 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>5530</v>
+        <v>5529</v>
       </c>
       <c r="O67" t="n">
-        <v>5530</v>
+        <v>5529</v>
       </c>
       <c r="U67" t="inlineStr">
         <is>
@@ -15544,13 +15544,13 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>5421</v>
+        <v>5493</v>
       </c>
       <c r="O76" t="n">
-        <v>5421</v>
+        <v>5493</v>
       </c>
       <c r="R76" t="n">
-        <v>10.50573495687668</v>
+        <v>10.64526879138971</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -15703,10 +15703,10 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>5421</v>
+        <v>5493</v>
       </c>
       <c r="O77" t="n">
-        <v>5421</v>
+        <v>5493</v>
       </c>
       <c r="U77" t="inlineStr">
         <is>
@@ -17533,13 +17533,13 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>462</v>
+        <v>1020</v>
       </c>
       <c r="O86" t="n">
-        <v>462</v>
+        <v>1020</v>
       </c>
       <c r="R86" t="n">
-        <v>0.8953421047919251</v>
+        <v>1.976729322267887</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
@@ -17692,10 +17692,10 @@
         </is>
       </c>
       <c r="N87" t="n">
-        <v>462</v>
+        <v>1020</v>
       </c>
       <c r="O87" t="n">
-        <v>462</v>
+        <v>1020</v>
       </c>
       <c r="U87" t="inlineStr">
         <is>
@@ -18037,7 +18037,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>38013</v>
+        <v>38642</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d227/2026-2029.xlsx
+++ b/diseases/d227/2026-2029.xlsx
@@ -13555,13 +13555,13 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>5529</v>
+        <v>5527</v>
       </c>
       <c r="O66" t="n">
-        <v>5529</v>
+        <v>5527</v>
       </c>
       <c r="R66" t="n">
-        <v>10.71503570864622</v>
+        <v>10.71115976879864</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -13714,10 +13714,10 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>5529</v>
+        <v>5527</v>
       </c>
       <c r="O67" t="n">
-        <v>5529</v>
+        <v>5527</v>
       </c>
       <c r="U67" t="inlineStr">
         <is>
@@ -15544,13 +15544,13 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>5493</v>
+        <v>5494</v>
       </c>
       <c r="O76" t="n">
-        <v>5493</v>
+        <v>5494</v>
       </c>
       <c r="R76" t="n">
-        <v>10.64526879138971</v>
+        <v>10.6472067613135</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -15703,10 +15703,10 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>5493</v>
+        <v>5494</v>
       </c>
       <c r="O77" t="n">
-        <v>5493</v>
+        <v>5494</v>
       </c>
       <c r="U77" t="inlineStr">
         <is>
@@ -17494,12 +17494,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -17524,22 +17524,25 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N86" t="n">
-        <v>1020</v>
+        <v>16</v>
       </c>
       <c r="O86" t="n">
-        <v>1020</v>
+        <v>16</v>
+      </c>
+      <c r="P86" t="n">
+        <v>16</v>
       </c>
       <c r="R86" t="n">
-        <v>1.976729322267887</v>
+        <v>0.01306893452105226</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
@@ -17548,12 +17551,12 @@
       </c>
       <c r="U86" t="inlineStr">
         <is>
-          <t>SER_KR_CRE</t>
+          <t>SER_JP_CRE_WEEKLY</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO86" t="inlineStr">
@@ -17573,7 +17576,7 @@
       </c>
       <c r="AS86" t="inlineStr">
         <is>
-          <t>SER_KR_CRE</t>
+          <t>SER_JP_CRE_WEEKLY</t>
         </is>
       </c>
       <c r="AT86" t="n">
@@ -17586,42 +17589,42 @@
       </c>
       <c r="AV86" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA86" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB86" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC86" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -17653,12 +17656,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -17683,38 +17686,41 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N87" t="n">
-        <v>1020</v>
+        <v>16</v>
       </c>
       <c r="O87" t="n">
-        <v>1020</v>
+        <v>16</v>
+      </c>
+      <c r="P87" t="n">
+        <v>16</v>
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>SER_KR_CRE</t>
+          <t>SER_JP_CRE_WEEKLY</t>
         </is>
       </c>
       <c r="V87" t="inlineStr">
         <is>
-          <t>SER_KR_CRE</t>
+          <t>SER_JP_CRE_WEEKLY</t>
         </is>
       </c>
       <c r="W87" t="inlineStr">
         <is>
-          <t>SRC_KR_KDCA</t>
+          <t>SRC_JP_NIID</t>
         </is>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>카바페넴내성장내세균목(CRE) 감염증</t>
+          <t>Carbapenem-resistant Enterobacterales infection</t>
         </is>
       </c>
       <c r="Y87" t="inlineStr">
@@ -17729,7 +17735,7 @@
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
@@ -17739,7 +17745,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>country:KR:national</t>
+          <t>country:JP:national</t>
         </is>
       </c>
       <c r="AD87" t="inlineStr">
@@ -17779,7 +17785,7 @@
       </c>
       <c r="AK87" t="inlineStr">
         <is>
-          <t>Korea KDCA carbapenem-resistant Enterobacterales infection category.</t>
+          <t>Japan NIID carbapenem-resistant Enterobacterales infection notifications.</t>
         </is>
       </c>
       <c r="AM87" t="inlineStr">
@@ -17807,7 +17813,7 @@
       </c>
       <c r="AS87" t="inlineStr">
         <is>
-          <t>SER_KR_CRE</t>
+          <t>SER_JP_CRE_WEEKLY</t>
         </is>
       </c>
       <c r="AT87" t="n">
@@ -17820,40 +17826,433 @@
       </c>
       <c r="AV87" t="inlineStr">
         <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA87" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB87" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC87" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>D227</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>carbapenem-resistant-enterobacterales-infection</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Carbapenem-resistant Enterobacterales infection</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>D227</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Carbapenem-resistant Enterobacterales infection</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>碳青霉烯耐药肠杆菌目细菌感染</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N88" t="n">
+        <v>1161</v>
+      </c>
+      <c r="O88" t="n">
+        <v>1161</v>
+      </c>
+      <c r="R88" t="n">
+        <v>2.249983081522565</v>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>SER_KR_CRE</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO88" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP88" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ88" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS88" t="inlineStr">
+        <is>
+          <t>SER_KR_CRE</t>
+        </is>
+      </c>
+      <c r="AT88" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU88" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV88" t="inlineStr">
+        <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW87" t="inlineStr">
+      <c r="AW88" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX87" t="inlineStr">
+      <c r="AX88" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY87" t="inlineStr">
+      <c r="AY88" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ87" t="inlineStr">
+      <c r="AZ88" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA87" t="inlineStr">
+      <c r="BA88" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB87" t="inlineStr">
+      <c r="BB88" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC87" t="inlineStr">
+      <c r="BC88" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>D227</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>carbapenem-resistant-enterobacterales-infection</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Carbapenem-resistant Enterobacterales infection</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>D227</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Carbapenem-resistant Enterobacterales infection</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>碳青霉烯耐药肠杆菌目细菌感染</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N89" t="n">
+        <v>1161</v>
+      </c>
+      <c r="O89" t="n">
+        <v>1161</v>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>SER_KR_CRE</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>SER_KR_CRE</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>SRC_KR_KDCA</t>
+        </is>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>카바페넴내성장내세균목(CRE) 감염증</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>country:KR:national</t>
+        </is>
+      </c>
+      <c r="AD89" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE89" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF89" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG89" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH89" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI89" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ89" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK89" t="inlineStr">
+        <is>
+          <t>Korea KDCA carbapenem-resistant Enterobacterales infection category.</t>
+        </is>
+      </c>
+      <c r="AM89" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN89" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO89" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP89" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ89" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS89" t="inlineStr">
+        <is>
+          <t>SER_KR_CRE</t>
+        </is>
+      </c>
+      <c r="AT89" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU89" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV89" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA89" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB89" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC89" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -17975,7 +18374,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10">
@@ -17985,7 +18384,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="11">
@@ -18005,7 +18404,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13">
@@ -18037,7 +18436,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>38642</v>
+        <v>38798</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d227/2026-2029.xlsx
+++ b/diseases/d227/2026-2029.xlsx
@@ -13555,13 +13555,13 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>5527</v>
+        <v>5530</v>
       </c>
       <c r="O66" t="n">
-        <v>5527</v>
+        <v>5530</v>
       </c>
       <c r="R66" t="n">
-        <v>10.71115976879864</v>
+        <v>10.71697367857001</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -13714,10 +13714,10 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>5527</v>
+        <v>5530</v>
       </c>
       <c r="O67" t="n">
-        <v>5527</v>
+        <v>5530</v>
       </c>
       <c r="U67" t="inlineStr">
         <is>
@@ -15544,13 +15544,13 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>5494</v>
+        <v>5556</v>
       </c>
       <c r="O76" t="n">
-        <v>5494</v>
+        <v>5556</v>
       </c>
       <c r="R76" t="n">
-        <v>10.6472067613135</v>
+        <v>10.76736089658861</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -15703,10 +15703,10 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>5494</v>
+        <v>5556</v>
       </c>
       <c r="O77" t="n">
-        <v>5494</v>
+        <v>5556</v>
       </c>
       <c r="U77" t="inlineStr">
         <is>
@@ -17932,13 +17932,13 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>1161</v>
+        <v>1529</v>
       </c>
       <c r="O88" t="n">
-        <v>1161</v>
+        <v>1529</v>
       </c>
       <c r="R88" t="n">
-        <v>2.249983081522565</v>
+        <v>2.963156013478038</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
@@ -18091,10 +18091,10 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>1161</v>
+        <v>1529</v>
       </c>
       <c r="O89" t="n">
-        <v>1161</v>
+        <v>1529</v>
       </c>
       <c r="U89" t="inlineStr">
         <is>
@@ -18436,7 +18436,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>38798</v>
+        <v>39231</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d227/2026-2029.xlsx
+++ b/diseases/d227/2026-2029.xlsx
@@ -13555,13 +13555,13 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>5530</v>
+        <v>5527</v>
       </c>
       <c r="O66" t="n">
-        <v>5530</v>
+        <v>5527</v>
       </c>
       <c r="R66" t="n">
-        <v>10.71697367857001</v>
+        <v>10.71115976879864</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -13714,10 +13714,10 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>5530</v>
+        <v>5527</v>
       </c>
       <c r="O67" t="n">
-        <v>5530</v>
+        <v>5527</v>
       </c>
       <c r="U67" t="inlineStr">
         <is>
@@ -15544,13 +15544,13 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>5556</v>
+        <v>5553</v>
       </c>
       <c r="O76" t="n">
-        <v>5556</v>
+        <v>5553</v>
       </c>
       <c r="R76" t="n">
-        <v>10.76736089658861</v>
+        <v>10.76154698681723</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -15703,10 +15703,10 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>5556</v>
+        <v>5553</v>
       </c>
       <c r="O77" t="n">
-        <v>5556</v>
+        <v>5553</v>
       </c>
       <c r="U77" t="inlineStr">
         <is>
@@ -17932,13 +17932,13 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>1529</v>
+        <v>1830</v>
       </c>
       <c r="O88" t="n">
-        <v>1529</v>
+        <v>1830</v>
       </c>
       <c r="R88" t="n">
-        <v>2.963156013478038</v>
+        <v>3.546484960539444</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
@@ -18091,10 +18091,10 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>1529</v>
+        <v>1830</v>
       </c>
       <c r="O89" t="n">
-        <v>1529</v>
+        <v>1830</v>
       </c>
       <c r="U89" t="inlineStr">
         <is>
@@ -18436,7 +18436,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>39231</v>
+        <v>39526</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d227/2026-2029.xlsx
+++ b/diseases/d227/2026-2029.xlsx
@@ -15544,13 +15544,13 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>5553</v>
+        <v>5554</v>
       </c>
       <c r="O76" t="n">
-        <v>5553</v>
+        <v>5554</v>
       </c>
       <c r="R76" t="n">
-        <v>10.76154698681723</v>
+        <v>10.76348495674102</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -15703,10 +15703,10 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>5553</v>
+        <v>5554</v>
       </c>
       <c r="O77" t="n">
-        <v>5553</v>
+        <v>5554</v>
       </c>
       <c r="U77" t="inlineStr">
         <is>
@@ -17932,13 +17932,13 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>1830</v>
+        <v>1853</v>
       </c>
       <c r="O88" t="n">
-        <v>1830</v>
+        <v>1853</v>
       </c>
       <c r="R88" t="n">
-        <v>3.546484960539444</v>
+        <v>3.591058268786661</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
@@ -18091,10 +18091,10 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>1830</v>
+        <v>1853</v>
       </c>
       <c r="O89" t="n">
-        <v>1830</v>
+        <v>1853</v>
       </c>
       <c r="U89" t="inlineStr">
         <is>
@@ -18436,7 +18436,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>39526</v>
+        <v>39550</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d227/2026-2029.xlsx
+++ b/diseases/d227/2026-2029.xlsx
@@ -15544,13 +15544,13 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>5554</v>
+        <v>5548</v>
       </c>
       <c r="O76" t="n">
-        <v>5554</v>
+        <v>5548</v>
       </c>
       <c r="R76" t="n">
-        <v>10.76348495674102</v>
+        <v>10.75185713719827</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -15703,10 +15703,10 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>5554</v>
+        <v>5548</v>
       </c>
       <c r="O77" t="n">
-        <v>5554</v>
+        <v>5548</v>
       </c>
       <c r="U77" t="inlineStr">
         <is>
@@ -17932,13 +17932,13 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>1853</v>
+        <v>2203</v>
       </c>
       <c r="O88" t="n">
-        <v>1853</v>
+        <v>2203</v>
       </c>
       <c r="R88" t="n">
-        <v>3.591058268786661</v>
+        <v>4.269347742113877</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
@@ -18091,10 +18091,10 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>1853</v>
+        <v>2203</v>
       </c>
       <c r="O89" t="n">
-        <v>1853</v>
+        <v>2203</v>
       </c>
       <c r="U89" t="inlineStr">
         <is>
@@ -18255,6 +18255,405 @@
       <c r="BC89" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>D227</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>carbapenem-resistant-enterobacterales-infection</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Carbapenem-resistant Enterobacterales infection</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>D227</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Carbapenem-resistant Enterobacterales infection</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>碳青霉烯耐药肠杆菌目细菌感染</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N90" t="n">
+        <v>11</v>
+      </c>
+      <c r="O90" t="n">
+        <v>11</v>
+      </c>
+      <c r="P90" t="n">
+        <v>11</v>
+      </c>
+      <c r="R90" t="n">
+        <v>0.00898489248322343</v>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>SER_JP_CRE_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO90" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP90" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ90" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS90" t="inlineStr">
+        <is>
+          <t>SER_JP_CRE_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT90" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU90" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV90" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA90" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB90" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC90" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>D227</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>carbapenem-resistant-enterobacterales-infection</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Carbapenem-resistant Enterobacterales infection</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>D227</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Carbapenem-resistant Enterobacterales infection</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>碳青霉烯耐药肠杆菌目细菌感染</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N91" t="n">
+        <v>11</v>
+      </c>
+      <c r="O91" t="n">
+        <v>11</v>
+      </c>
+      <c r="P91" t="n">
+        <v>11</v>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>SER_JP_CRE_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>SER_JP_CRE_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>Carbapenem-resistant Enterobacterales infection</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD91" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE91" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF91" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG91" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH91" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI91" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ91" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK91" t="inlineStr">
+        <is>
+          <t>Japan NIID carbapenem-resistant Enterobacterales infection notifications.</t>
+        </is>
+      </c>
+      <c r="AM91" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN91" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO91" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP91" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ91" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS91" t="inlineStr">
+        <is>
+          <t>SER_JP_CRE_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT91" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU91" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV91" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA91" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB91" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC91" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -18291,7 +18690,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18773,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10">
@@ -18384,7 +18783,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11">
@@ -18404,7 +18803,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13">
@@ -18436,7 +18835,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>39550</v>
+        <v>39905</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d227/2026-2029.xlsx
+++ b/diseases/d227/2026-2029.xlsx
@@ -13555,13 +13555,13 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>5527</v>
+        <v>5522</v>
       </c>
       <c r="O66" t="n">
-        <v>5527</v>
+        <v>5522</v>
       </c>
       <c r="R66" t="n">
-        <v>10.71115976879864</v>
+        <v>10.70146991917968</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -13714,10 +13714,10 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>5527</v>
+        <v>5522</v>
       </c>
       <c r="O67" t="n">
-        <v>5527</v>
+        <v>5522</v>
       </c>
       <c r="U67" t="inlineStr">
         <is>
@@ -15544,13 +15544,13 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>5548</v>
+        <v>5546</v>
       </c>
       <c r="O76" t="n">
-        <v>5548</v>
+        <v>5546</v>
       </c>
       <c r="R76" t="n">
-        <v>10.75185713719827</v>
+        <v>10.74798119735069</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -15703,10 +15703,10 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>5548</v>
+        <v>5546</v>
       </c>
       <c r="O77" t="n">
-        <v>5548</v>
+        <v>5546</v>
       </c>
       <c r="U77" t="inlineStr">
         <is>
@@ -17932,13 +17932,13 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>2203</v>
+        <v>2567</v>
       </c>
       <c r="O88" t="n">
-        <v>2203</v>
+        <v>2567</v>
       </c>
       <c r="R88" t="n">
-        <v>4.269347742113877</v>
+        <v>4.974768794374182</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
@@ -18091,10 +18091,10 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>2203</v>
+        <v>2567</v>
       </c>
       <c r="O89" t="n">
-        <v>2203</v>
+        <v>2567</v>
       </c>
       <c r="U89" t="inlineStr">
         <is>
@@ -18835,7 +18835,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>39905</v>
+        <v>40262</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d227/2026-2029.xlsx
+++ b/diseases/d227/2026-2029.xlsx
@@ -13555,13 +13555,13 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>5522</v>
+        <v>5514</v>
       </c>
       <c r="O66" t="n">
-        <v>5522</v>
+        <v>5514</v>
       </c>
       <c r="R66" t="n">
-        <v>10.70146991917968</v>
+        <v>10.68596615978934</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -13714,10 +13714,10 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>5522</v>
+        <v>5514</v>
       </c>
       <c r="O67" t="n">
-        <v>5522</v>
+        <v>5514</v>
       </c>
       <c r="U67" t="inlineStr">
         <is>
@@ -15544,13 +15544,13 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>5546</v>
+        <v>5569</v>
       </c>
       <c r="O76" t="n">
-        <v>5546</v>
+        <v>5569</v>
       </c>
       <c r="R76" t="n">
-        <v>10.74798119735069</v>
+        <v>10.7925545055979</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -15703,10 +15703,10 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>5546</v>
+        <v>5569</v>
       </c>
       <c r="O77" t="n">
-        <v>5546</v>
+        <v>5569</v>
       </c>
       <c r="U77" t="inlineStr">
         <is>
@@ -17932,13 +17932,13 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>2567</v>
+        <v>3140</v>
       </c>
       <c r="O88" t="n">
-        <v>2567</v>
+        <v>3140</v>
       </c>
       <c r="R88" t="n">
-        <v>4.974768794374182</v>
+        <v>6.085225560707024</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
@@ -18091,10 +18091,10 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>2567</v>
+        <v>3140</v>
       </c>
       <c r="O89" t="n">
-        <v>2567</v>
+        <v>3140</v>
       </c>
       <c r="U89" t="inlineStr">
         <is>
@@ -18835,7 +18835,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>40262</v>
+        <v>40850</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d227/2026-2029.xlsx
+++ b/diseases/d227/2026-2029.xlsx
@@ -13555,13 +13555,13 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>5514</v>
+        <v>5513</v>
       </c>
       <c r="O66" t="n">
-        <v>5514</v>
+        <v>5513</v>
       </c>
       <c r="R66" t="n">
-        <v>10.68596615978934</v>
+        <v>10.68402818986555</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -13714,10 +13714,10 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>5514</v>
+        <v>5513</v>
       </c>
       <c r="O67" t="n">
-        <v>5514</v>
+        <v>5513</v>
       </c>
       <c r="U67" t="inlineStr">
         <is>
@@ -17932,13 +17932,13 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>3140</v>
+        <v>3374</v>
       </c>
       <c r="O88" t="n">
-        <v>3140</v>
+        <v>3374</v>
       </c>
       <c r="R88" t="n">
-        <v>6.085225560707024</v>
+        <v>6.538710522874362</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
@@ -18091,10 +18091,10 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>3140</v>
+        <v>3374</v>
       </c>
       <c r="O89" t="n">
-        <v>3140</v>
+        <v>3374</v>
       </c>
       <c r="U89" t="inlineStr">
         <is>
@@ -18835,7 +18835,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>40850</v>
+        <v>41083</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d227/2026-2029.xlsx
+++ b/diseases/d227/2026-2029.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4205,7 +4205,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4607,7 +4607,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5009,7 +5009,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5402,7 +5402,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5804,7 +5804,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6206,7 +6206,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6608,7 +6608,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7403,7 +7403,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7805,7 +7805,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8207,7 +8207,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8609,7 +8609,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -9011,7 +9011,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9404,7 +9404,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9806,7 +9806,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10208,7 +10208,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10610,7 +10610,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11012,7 +11012,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11414,7 +11414,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11807,7 +11807,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12206,7 +12206,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12605,7 +12605,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -13004,7 +13004,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13403,7 +13403,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13555,13 +13555,13 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>5513</v>
+        <v>5512</v>
       </c>
       <c r="O66" t="n">
-        <v>5513</v>
+        <v>5512</v>
       </c>
       <c r="R66" t="n">
-        <v>10.68402818986555</v>
+        <v>10.68209021994176</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -13714,10 +13714,10 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>5513</v>
+        <v>5512</v>
       </c>
       <c r="O67" t="n">
-        <v>5513</v>
+        <v>5512</v>
       </c>
       <c r="U67" t="inlineStr">
         <is>
@@ -13796,7 +13796,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14195,7 +14195,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14993,7 +14993,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15392,7 +15392,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15544,13 +15544,13 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>5569</v>
+        <v>5568</v>
       </c>
       <c r="O76" t="n">
-        <v>5569</v>
+        <v>5568</v>
       </c>
       <c r="R76" t="n">
-        <v>10.7925545055979</v>
+        <v>10.79061653567411</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -15703,10 +15703,10 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>5569</v>
+        <v>5568</v>
       </c>
       <c r="O77" t="n">
-        <v>5569</v>
+        <v>5568</v>
       </c>
       <c r="U77" t="inlineStr">
         <is>
@@ -15785,7 +15785,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -16184,7 +16184,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16583,7 +16583,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16982,7 +16982,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17381,7 +17381,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17780,7 +17780,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -17932,13 +17932,13 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>3374</v>
+        <v>3731</v>
       </c>
       <c r="O88" t="n">
-        <v>3374</v>
+        <v>3731</v>
       </c>
       <c r="R88" t="n">
-        <v>6.538710522874362</v>
+        <v>7.230565785668123</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
@@ -18091,10 +18091,10 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>3374</v>
+        <v>3731</v>
       </c>
       <c r="O89" t="n">
-        <v>3374</v>
+        <v>3731</v>
       </c>
       <c r="U89" t="inlineStr">
         <is>
@@ -18173,7 +18173,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18572,7 +18572,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -18652,6 +18652,405 @@
         </is>
       </c>
       <c r="BC91" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>D227</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>carbapenem-resistant-enterobacterales-infection</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Carbapenem-resistant Enterobacterales infection</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>D227</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Carbapenem-resistant Enterobacterales infection</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>碳青霉烯耐药肠杆菌目细菌感染</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N92" t="n">
+        <v>26</v>
+      </c>
+      <c r="O92" t="n">
+        <v>26</v>
+      </c>
+      <c r="P92" t="n">
+        <v>26</v>
+      </c>
+      <c r="R92" t="n">
+        <v>0.02123701859670992</v>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>SER_JP_CRE_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO92" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP92" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ92" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS92" t="inlineStr">
+        <is>
+          <t>SER_JP_CRE_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT92" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU92" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV92" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA92" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB92" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC92" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>D227</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>carbapenem-resistant-enterobacterales-infection</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Carbapenem-resistant Enterobacterales infection</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>D227</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Carbapenem-resistant Enterobacterales infection</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>碳青霉烯耐药肠杆菌目细菌感染</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N93" t="n">
+        <v>26</v>
+      </c>
+      <c r="O93" t="n">
+        <v>26</v>
+      </c>
+      <c r="P93" t="n">
+        <v>26</v>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>SER_JP_CRE_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>SER_JP_CRE_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>Carbapenem-resistant Enterobacterales infection</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD93" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE93" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF93" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG93" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH93" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI93" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ93" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK93" t="inlineStr">
+        <is>
+          <t>Japan NIID carbapenem-resistant Enterobacterales infection notifications.</t>
+        </is>
+      </c>
+      <c r="AM93" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN93" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO93" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP93" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ93" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS93" t="inlineStr">
+        <is>
+          <t>SER_JP_CRE_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT93" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU93" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV93" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA93" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB93" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC93" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -18690,7 +19089,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -18773,7 +19172,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10">
@@ -18783,7 +19182,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11">
@@ -18803,7 +19202,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13">
@@ -18835,7 +19234,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>41083</v>
+        <v>41464</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d227/2026-2029.xlsx
+++ b/diseases/d227/2026-2029.xlsx
@@ -17932,13 +17932,13 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>3731</v>
+        <v>3742</v>
       </c>
       <c r="O88" t="n">
-        <v>3731</v>
+        <v>3742</v>
       </c>
       <c r="R88" t="n">
-        <v>7.230565785668123</v>
+        <v>7.251883454829836</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
@@ -18091,10 +18091,10 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>3731</v>
+        <v>3742</v>
       </c>
       <c r="O89" t="n">
-        <v>3731</v>
+        <v>3742</v>
       </c>
       <c r="U89" t="inlineStr">
         <is>
@@ -19234,7 +19234,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>41464</v>
+        <v>41475</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d227/2026-2029.xlsx
+++ b/diseases/d227/2026-2029.xlsx
@@ -13555,13 +13555,13 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>5512</v>
+        <v>5507</v>
       </c>
       <c r="O66" t="n">
-        <v>5512</v>
+        <v>5507</v>
       </c>
       <c r="R66" t="n">
-        <v>10.68209021994176</v>
+        <v>10.6724003703228</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -13714,10 +13714,10 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>5512</v>
+        <v>5507</v>
       </c>
       <c r="O67" t="n">
-        <v>5512</v>
+        <v>5507</v>
       </c>
       <c r="U67" t="inlineStr">
         <is>
@@ -15544,13 +15544,13 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>5568</v>
+        <v>5561</v>
       </c>
       <c r="O76" t="n">
-        <v>5568</v>
+        <v>5561</v>
       </c>
       <c r="R76" t="n">
-        <v>10.79061653567411</v>
+        <v>10.77705074620757</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -15703,10 +15703,10 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>5568</v>
+        <v>5561</v>
       </c>
       <c r="O77" t="n">
-        <v>5568</v>
+        <v>5561</v>
       </c>
       <c r="U77" t="inlineStr">
         <is>
@@ -17932,13 +17932,13 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>3742</v>
+        <v>5122</v>
       </c>
       <c r="O88" t="n">
-        <v>3742</v>
+        <v>5122</v>
       </c>
       <c r="R88" t="n">
-        <v>7.251883454829836</v>
+        <v>9.92628194966286</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
@@ -18091,10 +18091,10 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>3742</v>
+        <v>5122</v>
       </c>
       <c r="O89" t="n">
-        <v>3742</v>
+        <v>5122</v>
       </c>
       <c r="U89" t="inlineStr">
         <is>
@@ -19053,6 +19053,798 @@
       <c r="BC93" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>D227</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>carbapenem-resistant-enterobacterales-infection</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Carbapenem-resistant Enterobacterales infection</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>D227</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Carbapenem-resistant Enterobacterales infection</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>碳青霉烯耐药肠杆菌目细菌感染</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N94" t="n">
+        <v>21</v>
+      </c>
+      <c r="O94" t="n">
+        <v>21</v>
+      </c>
+      <c r="P94" t="n">
+        <v>21</v>
+      </c>
+      <c r="R94" t="n">
+        <v>0.01715297655888109</v>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>SER_JP_CRE_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO94" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP94" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ94" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS94" t="inlineStr">
+        <is>
+          <t>SER_JP_CRE_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT94" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU94" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV94" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA94" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB94" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC94" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>D227</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>carbapenem-resistant-enterobacterales-infection</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Carbapenem-resistant Enterobacterales infection</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>D227</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Carbapenem-resistant Enterobacterales infection</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>碳青霉烯耐药肠杆菌目细菌感染</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N95" t="n">
+        <v>21</v>
+      </c>
+      <c r="O95" t="n">
+        <v>21</v>
+      </c>
+      <c r="P95" t="n">
+        <v>21</v>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>SER_JP_CRE_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>SER_JP_CRE_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>Carbapenem-resistant Enterobacterales infection</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD95" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE95" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF95" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG95" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH95" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI95" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ95" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK95" t="inlineStr">
+        <is>
+          <t>Japan NIID carbapenem-resistant Enterobacterales infection notifications.</t>
+        </is>
+      </c>
+      <c r="AM95" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN95" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO95" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP95" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ95" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS95" t="inlineStr">
+        <is>
+          <t>SER_JP_CRE_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT95" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV95" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA95" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB95" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC95" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>D227</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>carbapenem-resistant-enterobacterales-infection</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Carbapenem-resistant Enterobacterales infection</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>D227</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Carbapenem-resistant Enterobacterales infection</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>碳青霉烯耐药肠杆菌目细菌感染</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N96" t="n">
+        <v>214</v>
+      </c>
+      <c r="O96" t="n">
+        <v>214</v>
+      </c>
+      <c r="R96" t="n">
+        <v>0.4147255636914978</v>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>SER_KR_CRE</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO96" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP96" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ96" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS96" t="inlineStr">
+        <is>
+          <t>SER_KR_CRE</t>
+        </is>
+      </c>
+      <c r="AT96" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU96" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV96" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA96" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB96" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC96" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>D227</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>carbapenem-resistant-enterobacterales-infection</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Carbapenem-resistant Enterobacterales infection</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>D227</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Carbapenem-resistant Enterobacterales infection</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>碳青霉烯耐药肠杆菌目细菌感染</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N97" t="n">
+        <v>214</v>
+      </c>
+      <c r="O97" t="n">
+        <v>214</v>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>SER_KR_CRE</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>SER_KR_CRE</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>SRC_KR_KDCA</t>
+        </is>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>카바페넴내성장내세균목(CRE) 감염증</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>country:KR:national</t>
+        </is>
+      </c>
+      <c r="AD97" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE97" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF97" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG97" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH97" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI97" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ97" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK97" t="inlineStr">
+        <is>
+          <t>Korea KDCA carbapenem-resistant Enterobacterales infection category.</t>
+        </is>
+      </c>
+      <c r="AM97" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN97" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO97" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP97" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ97" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS97" t="inlineStr">
+        <is>
+          <t>SER_KR_CRE</t>
+        </is>
+      </c>
+      <c r="AT97" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV97" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA97" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB97" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC97" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -19089,7 +19881,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -19172,7 +19964,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10">
@@ -19182,7 +19974,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11">
@@ -19202,7 +19994,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13">
@@ -19234,7 +20026,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>41475</v>
+        <v>43078</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d227/2026-2029.xlsx
+++ b/diseases/d227/2026-2029.xlsx
@@ -15544,13 +15544,13 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>5561</v>
+        <v>5558</v>
       </c>
       <c r="O76" t="n">
-        <v>5561</v>
+        <v>5558</v>
       </c>
       <c r="R76" t="n">
-        <v>10.77705074620757</v>
+        <v>10.77123683643619</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -15703,10 +15703,10 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>5561</v>
+        <v>5558</v>
       </c>
       <c r="O77" t="n">
-        <v>5561</v>
+        <v>5558</v>
       </c>
       <c r="U77" t="inlineStr">
         <is>
@@ -17932,13 +17932,13 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>5122</v>
+        <v>5239</v>
       </c>
       <c r="O88" t="n">
-        <v>5122</v>
+        <v>5239</v>
       </c>
       <c r="R88" t="n">
-        <v>9.92628194966286</v>
+        <v>10.15302443074653</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
@@ -18091,10 +18091,10 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>5122</v>
+        <v>5239</v>
       </c>
       <c r="O89" t="n">
-        <v>5122</v>
+        <v>5239</v>
       </c>
       <c r="U89" t="inlineStr">
         <is>
@@ -19483,12 +19483,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -19513,22 +19513,25 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N96" t="n">
-        <v>214</v>
+        <v>9</v>
       </c>
       <c r="O96" t="n">
-        <v>214</v>
+        <v>9</v>
+      </c>
+      <c r="P96" t="n">
+        <v>9</v>
       </c>
       <c r="R96" t="n">
-        <v>0.4147255636914978</v>
+        <v>0.007351275668091897</v>
       </c>
       <c r="S96" t="inlineStr">
         <is>
@@ -19537,12 +19540,12 @@
       </c>
       <c r="U96" t="inlineStr">
         <is>
-          <t>SER_KR_CRE</t>
+          <t>SER_JP_CRE_WEEKLY</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO96" t="inlineStr">
@@ -19562,7 +19565,7 @@
       </c>
       <c r="AS96" t="inlineStr">
         <is>
-          <t>SER_KR_CRE</t>
+          <t>SER_JP_CRE_WEEKLY</t>
         </is>
       </c>
       <c r="AT96" t="n">
@@ -19575,42 +19578,42 @@
       </c>
       <c r="AV96" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA96" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB96" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC96" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -19642,12 +19645,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -19672,38 +19675,41 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N97" t="n">
-        <v>214</v>
+        <v>9</v>
       </c>
       <c r="O97" t="n">
-        <v>214</v>
+        <v>9</v>
+      </c>
+      <c r="P97" t="n">
+        <v>9</v>
       </c>
       <c r="U97" t="inlineStr">
         <is>
-          <t>SER_KR_CRE</t>
+          <t>SER_JP_CRE_WEEKLY</t>
         </is>
       </c>
       <c r="V97" t="inlineStr">
         <is>
-          <t>SER_KR_CRE</t>
+          <t>SER_JP_CRE_WEEKLY</t>
         </is>
       </c>
       <c r="W97" t="inlineStr">
         <is>
-          <t>SRC_KR_KDCA</t>
+          <t>SRC_JP_NIID</t>
         </is>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>카바페넴내성장내세균목(CRE) 감염증</t>
+          <t>Carbapenem-resistant Enterobacterales infection</t>
         </is>
       </c>
       <c r="Y97" t="inlineStr">
@@ -19718,7 +19724,7 @@
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
@@ -19728,7 +19734,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>country:KR:national</t>
+          <t>country:JP:national</t>
         </is>
       </c>
       <c r="AD97" t="inlineStr">
@@ -19768,7 +19774,7 @@
       </c>
       <c r="AK97" t="inlineStr">
         <is>
-          <t>Korea KDCA carbapenem-resistant Enterobacterales infection category.</t>
+          <t>Japan NIID carbapenem-resistant Enterobacterales infection notifications.</t>
         </is>
       </c>
       <c r="AM97" t="inlineStr">
@@ -19796,7 +19802,7 @@
       </c>
       <c r="AS97" t="inlineStr">
         <is>
-          <t>SER_KR_CRE</t>
+          <t>SER_JP_CRE_WEEKLY</t>
         </is>
       </c>
       <c r="AT97" t="n">
@@ -19809,40 +19815,433 @@
       </c>
       <c r="AV97" t="inlineStr">
         <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA97" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB97" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC97" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>D227</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>carbapenem-resistant-enterobacterales-infection</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Carbapenem-resistant Enterobacterales infection</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>D227</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Carbapenem-resistant Enterobacterales infection</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>碳青霉烯耐药肠杆菌目细菌感染</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N98" t="n">
+        <v>528</v>
+      </c>
+      <c r="O98" t="n">
+        <v>528</v>
+      </c>
+      <c r="R98" t="n">
+        <v>1.0232481197622</v>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>SER_KR_CRE</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO98" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP98" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ98" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS98" t="inlineStr">
+        <is>
+          <t>SER_KR_CRE</t>
+        </is>
+      </c>
+      <c r="AT98" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU98" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV98" t="inlineStr">
+        <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW97" t="inlineStr">
+      <c r="AW98" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX97" t="inlineStr">
+      <c r="AX98" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY97" t="inlineStr">
+      <c r="AY98" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ97" t="inlineStr">
+      <c r="AZ98" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA97" t="inlineStr">
+      <c r="BA98" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB97" t="inlineStr">
+      <c r="BB98" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC97" t="inlineStr">
+      <c r="BC98" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>D227</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>carbapenem-resistant-enterobacterales-infection</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Carbapenem-resistant Enterobacterales infection</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>D227</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Carbapenem-resistant Enterobacterales infection</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>碳青霉烯耐药肠杆菌目细菌感染</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N99" t="n">
+        <v>528</v>
+      </c>
+      <c r="O99" t="n">
+        <v>528</v>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>SER_KR_CRE</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>SER_KR_CRE</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>SRC_KR_KDCA</t>
+        </is>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>카바페넴내성장내세균목(CRE) 감염증</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>country:KR:national</t>
+        </is>
+      </c>
+      <c r="AD99" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE99" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF99" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG99" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH99" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI99" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ99" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK99" t="inlineStr">
+        <is>
+          <t>Korea KDCA carbapenem-resistant Enterobacterales infection category.</t>
+        </is>
+      </c>
+      <c r="AM99" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN99" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO99" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP99" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ99" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS99" t="inlineStr">
+        <is>
+          <t>SER_KR_CRE</t>
+        </is>
+      </c>
+      <c r="AT99" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU99" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV99" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA99" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB99" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC99" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -19964,7 +20363,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10">
@@ -19974,7 +20373,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="11">
@@ -19994,7 +20393,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13">
@@ -20026,7 +20425,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>43078</v>
+        <v>43515</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d227/2026-2029.xlsx
+++ b/diseases/d227/2026-2029.xlsx
@@ -15544,13 +15544,13 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>5558</v>
+        <v>5557</v>
       </c>
       <c r="O76" t="n">
-        <v>5558</v>
+        <v>5557</v>
       </c>
       <c r="R76" t="n">
-        <v>10.77123683643619</v>
+        <v>10.7692988665124</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -15703,10 +15703,10 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>5558</v>
+        <v>5557</v>
       </c>
       <c r="O77" t="n">
-        <v>5558</v>
+        <v>5557</v>
       </c>
       <c r="U77" t="inlineStr">
         <is>
@@ -17932,13 +17932,13 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>5239</v>
+        <v>5233</v>
       </c>
       <c r="O88" t="n">
-        <v>5239</v>
+        <v>5233</v>
       </c>
       <c r="R88" t="n">
-        <v>10.15302443074653</v>
+        <v>10.14139661120378</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
@@ -18091,10 +18091,10 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>5239</v>
+        <v>5233</v>
       </c>
       <c r="O89" t="n">
-        <v>5239</v>
+        <v>5233</v>
       </c>
       <c r="U89" t="inlineStr">
         <is>
@@ -19921,13 +19921,13 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>528</v>
+        <v>694</v>
       </c>
       <c r="O98" t="n">
-        <v>528</v>
+        <v>694</v>
       </c>
       <c r="R98" t="n">
-        <v>1.0232481197622</v>
+        <v>1.34495112711168</v>
       </c>
       <c r="S98" t="inlineStr">
         <is>
@@ -20080,10 +20080,10 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>528</v>
+        <v>694</v>
       </c>
       <c r="O99" t="n">
-        <v>528</v>
+        <v>694</v>
       </c>
       <c r="U99" t="inlineStr">
         <is>
@@ -20425,7 +20425,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>43515</v>
+        <v>43674</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d227/2026-2029.xlsx
+++ b/diseases/d227/2026-2029.xlsx
@@ -17932,13 +17932,13 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>5233</v>
+        <v>5240</v>
       </c>
       <c r="O88" t="n">
-        <v>5233</v>
+        <v>5240</v>
       </c>
       <c r="R88" t="n">
-        <v>10.14139661120378</v>
+        <v>10.15496240067032</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
@@ -18091,10 +18091,10 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>5233</v>
+        <v>5240</v>
       </c>
       <c r="O89" t="n">
-        <v>5233</v>
+        <v>5240</v>
       </c>
       <c r="U89" t="inlineStr">
         <is>
@@ -19921,13 +19921,13 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>694</v>
+        <v>889</v>
       </c>
       <c r="O98" t="n">
-        <v>694</v>
+        <v>889</v>
       </c>
       <c r="R98" t="n">
-        <v>1.34495112711168</v>
+        <v>1.722855262251129</v>
       </c>
       <c r="S98" t="inlineStr">
         <is>
@@ -20080,10 +20080,10 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>694</v>
+        <v>889</v>
       </c>
       <c r="O99" t="n">
-        <v>694</v>
+        <v>889</v>
       </c>
       <c r="U99" t="inlineStr">
         <is>
@@ -20425,7 +20425,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>43674</v>
+        <v>43876</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d227/2026-2029.xlsx
+++ b/diseases/d227/2026-2029.xlsx
@@ -15544,13 +15544,13 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>5557</v>
+        <v>5554</v>
       </c>
       <c r="O76" t="n">
-        <v>5557</v>
+        <v>5554</v>
       </c>
       <c r="R76" t="n">
-        <v>10.7692988665124</v>
+        <v>10.76348495674102</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -15703,10 +15703,10 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>5557</v>
+        <v>5554</v>
       </c>
       <c r="O77" t="n">
-        <v>5557</v>
+        <v>5554</v>
       </c>
       <c r="U77" t="inlineStr">
         <is>
@@ -19921,13 +19921,13 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>889</v>
+        <v>1352</v>
       </c>
       <c r="O98" t="n">
-        <v>889</v>
+        <v>1352</v>
       </c>
       <c r="R98" t="n">
-        <v>1.722855262251129</v>
+        <v>2.620135336966846</v>
       </c>
       <c r="S98" t="inlineStr">
         <is>
@@ -20080,10 +20080,10 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>889</v>
+        <v>1352</v>
       </c>
       <c r="O99" t="n">
-        <v>889</v>
+        <v>1352</v>
       </c>
       <c r="U99" t="inlineStr">
         <is>
@@ -20425,7 +20425,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>43876</v>
+        <v>44336</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d227/2026-2029.xlsx
+++ b/diseases/d227/2026-2029.xlsx
@@ -15544,13 +15544,13 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>5554</v>
+        <v>5553</v>
       </c>
       <c r="O76" t="n">
-        <v>5554</v>
+        <v>5553</v>
       </c>
       <c r="R76" t="n">
-        <v>10.76348495674102</v>
+        <v>10.76154698681723</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -15703,10 +15703,10 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>5554</v>
+        <v>5553</v>
       </c>
       <c r="O77" t="n">
-        <v>5554</v>
+        <v>5553</v>
       </c>
       <c r="U77" t="inlineStr">
         <is>
@@ -17932,13 +17932,13 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>5240</v>
+        <v>5229</v>
       </c>
       <c r="O88" t="n">
-        <v>5240</v>
+        <v>5229</v>
       </c>
       <c r="R88" t="n">
-        <v>10.15496240067032</v>
+        <v>10.13364473150861</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
@@ -18091,10 +18091,10 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>5240</v>
+        <v>5229</v>
       </c>
       <c r="O89" t="n">
-        <v>5240</v>
+        <v>5229</v>
       </c>
       <c r="U89" t="inlineStr">
         <is>
@@ -19921,13 +19921,13 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>1352</v>
+        <v>1852</v>
       </c>
       <c r="O98" t="n">
-        <v>1352</v>
+        <v>1852</v>
       </c>
       <c r="R98" t="n">
-        <v>2.620135336966846</v>
+        <v>3.589120298862869</v>
       </c>
       <c r="S98" t="inlineStr">
         <is>
@@ -20080,10 +20080,10 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>1352</v>
+        <v>1852</v>
       </c>
       <c r="O99" t="n">
-        <v>1352</v>
+        <v>1852</v>
       </c>
       <c r="U99" t="inlineStr">
         <is>
@@ -20244,6 +20244,405 @@
       <c r="BC99" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>D227</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>carbapenem-resistant-enterobacterales-infection</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Carbapenem-resistant Enterobacterales infection</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>D227</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Carbapenem-resistant Enterobacterales infection</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>碳青霉烯耐药肠杆菌目细菌感染</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N100" t="n">
+        <v>10</v>
+      </c>
+      <c r="O100" t="n">
+        <v>10</v>
+      </c>
+      <c r="P100" t="n">
+        <v>10</v>
+      </c>
+      <c r="R100" t="n">
+        <v>0.008168084075657663</v>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>SER_JP_CRE_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO100" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP100" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ100" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS100" t="inlineStr">
+        <is>
+          <t>SER_JP_CRE_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT100" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV100" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA100" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB100" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC100" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>D227</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>carbapenem-resistant-enterobacterales-infection</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Carbapenem-resistant Enterobacterales infection</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>D227</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Carbapenem-resistant Enterobacterales infection</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>碳青霉烯耐药肠杆菌目细菌感染</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N101" t="n">
+        <v>10</v>
+      </c>
+      <c r="O101" t="n">
+        <v>10</v>
+      </c>
+      <c r="P101" t="n">
+        <v>10</v>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>SER_JP_CRE_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>SER_JP_CRE_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>Carbapenem-resistant Enterobacterales infection</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD101" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE101" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF101" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG101" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH101" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI101" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ101" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK101" t="inlineStr">
+        <is>
+          <t>Japan NIID carbapenem-resistant Enterobacterales infection notifications.</t>
+        </is>
+      </c>
+      <c r="AM101" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN101" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO101" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP101" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ101" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS101" t="inlineStr">
+        <is>
+          <t>SER_JP_CRE_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT101" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU101" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV101" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA101" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB101" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC101" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -20280,7 +20679,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -20363,7 +20762,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10">
@@ -20373,7 +20772,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11">
@@ -20393,7 +20792,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13">
@@ -20425,7 +20824,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>44336</v>
+        <v>44834</v>
       </c>
     </row>
     <row r="16">
